--- a/rsv_psa_summary.xlsx
+++ b/rsv_psa_summary.xlsx
@@ -389,16 +389,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>-28314833877.62812</v>
+        <v>16536023888.18177</v>
       </c>
       <c r="C2">
         <v>405506.2451079012</v>
       </c>
       <c r="D2">
-        <v>-69825.88855097366</v>
+        <v>40778.71571073263</v>
       </c>
       <c r="E2">
-        <v>24612.69732873837</v>
+        <v>-6277.426248120376</v>
       </c>
     </row>
     <row r="3">
@@ -408,16 +408,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-25754807768.30886</v>
+        <v>18661806720.15842</v>
       </c>
       <c r="C3">
         <v>409527.0926813115</v>
       </c>
       <c r="D3">
-        <v>-62889.14269305965</v>
+        <v>45569.16270904888</v>
       </c>
       <c r="E3">
-        <v>-8454.347461371728</v>
+        <v>3191.382217312619</v>
       </c>
     </row>
   </sheetData>
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>50.2</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="3">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>50.1</v>
+        <v>49.3</v>
       </c>
     </row>
   </sheetData>

--- a/rsv_psa_summary.xlsx
+++ b/rsv_psa_summary.xlsx
@@ -7,8 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Mean ICER" sheetId="1" r:id="rId1"/>
-    <sheet name="Pct Cost-Effective" sheetId="2" r:id="rId2"/>
+    <sheet name="INMB Summary" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -352,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -363,22 +362,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_inc_cost</t>
+          <t>threshold</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_inc_qaly</t>
+          <t>mean_inmb</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_icer</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mean_sim_icer</t>
+          <t>pct_cost_effective</t>
         </is>
       </c>
     </row>
@@ -388,78 +382,70 @@
           <t>Arexvy</t>
         </is>
       </c>
-      <c r="B2">
-        <v>16536023888.18177</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>$100k</t>
+        </is>
       </c>
       <c r="C2">
-        <v>405506.2451079012</v>
+        <v>315352017942.6414</v>
       </c>
       <c r="D2">
-        <v>40778.71571073263</v>
-      </c>
-      <c r="E2">
-        <v>-6277.426248120376</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Arexvy</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>$150k</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>458985746471.0419</v>
+      </c>
+      <c r="D3">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Abrysvo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>18661806720.15842</v>
-      </c>
-      <c r="C3">
-        <v>409527.0926813115</v>
-      </c>
-      <c r="D3">
-        <v>45569.16270904888</v>
-      </c>
-      <c r="E3">
-        <v>3191.382217312619</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$100k</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>312375024695.7823</v>
+      </c>
+      <c r="D4">
+        <v>54</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>vaccine</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>pct_cost_effective</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Arexvy</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>49.3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Abrysvo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>49.3</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$150k</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>455751327453.3544</v>
+      </c>
+      <c r="D5">
+        <v>53.8</v>
       </c>
     </row>
   </sheetData>
